--- a/data/base/Backlog_24.xlsx
+++ b/data/base/Backlog_24.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\AppData\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D166C5-C2FA-414C-9BA4-CC95134D9A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17BDCCFE-83C6-44CA-9B53-8B90B8C1C356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="32">
   <si>
     <t>Status</t>
   </si>
@@ -130,10 +130,13 @@
     <t>Fabio Silva</t>
   </si>
   <si>
-    <t>Arthur Hassuma</t>
-  </si>
-  <si>
     <t>Lourival Silva</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Erick Silva</t>
   </si>
 </sst>
 </file>
@@ -183,7 +186,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,18 +196,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -281,30 +272,15 @@
     <xf numFmtId="17" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -639,20 +615,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.7109375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" style="6" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
@@ -691,42 +662,42 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="5">
         <v>2026</v>
       </c>
       <c r="D2" s="10">
         <v>24</v>
       </c>
-      <c r="E2" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F2" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G2" s="11">
-        <v>19299</v>
+      <c r="E2" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F2" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G2" s="5">
+        <v>16819</v>
       </c>
       <c r="H2" s="12">
-        <v>46195.583402777775</v>
-      </c>
-      <c r="I2" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="10" t="s">
+        <v>46157.643171296295</v>
+      </c>
+      <c r="I2" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,29 +710,29 @@
       <c r="D3" s="10">
         <v>24</v>
       </c>
-      <c r="E3" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F3" s="14">
+      <c r="E3" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F3" s="16">
         <v>46199</v>
       </c>
       <c r="G3" s="5">
-        <v>16819</v>
+        <v>18346</v>
       </c>
       <c r="H3" s="12">
-        <v>46157.643171296295</v>
-      </c>
-      <c r="I3" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J3" s="11" t="s">
+        <v>46178.538541666669</v>
+      </c>
+      <c r="I3" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -774,34 +745,34 @@
       <c r="D4" s="10">
         <v>24</v>
       </c>
-      <c r="E4" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F4" s="14">
+      <c r="E4" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F4" s="16">
         <v>46199</v>
       </c>
       <c r="G4" s="5">
-        <v>18346</v>
+        <v>18418</v>
       </c>
       <c r="H4" s="12">
-        <v>46178.538541666669</v>
-      </c>
-      <c r="I4" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J4" s="11" t="s">
+        <v>46178.708333333336</v>
+      </c>
+      <c r="I4" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J4" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5">
         <v>2026</v>
@@ -809,29 +780,29 @@
       <c r="D5" s="10">
         <v>24</v>
       </c>
-      <c r="E5" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="E5" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F5" s="16">
         <v>46199</v>
       </c>
       <c r="G5" s="5">
-        <v>18418</v>
+        <v>18276</v>
       </c>
       <c r="H5" s="12">
-        <v>46178.708333333336</v>
-      </c>
-      <c r="I5" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>13</v>
+        <v>46177.708333333336</v>
+      </c>
+      <c r="I5" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -844,165 +815,165 @@
       <c r="D6" s="10">
         <v>24</v>
       </c>
-      <c r="E6" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="E6" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F6" s="16">
         <v>46199</v>
       </c>
       <c r="G6" s="5">
-        <v>18276</v>
+        <v>18485</v>
       </c>
       <c r="H6" s="12">
-        <v>46177.708333333336</v>
-      </c>
-      <c r="I6" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>13</v>
+        <v>46181.62840277778</v>
+      </c>
+      <c r="I6" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="11">
         <v>2026</v>
       </c>
       <c r="D7" s="10">
         <v>24</v>
       </c>
-      <c r="E7" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F7" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G7" s="5">
-        <v>18485</v>
+      <c r="E7" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F7" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G7" s="11">
+        <v>18593</v>
       </c>
       <c r="H7" s="12">
-        <v>46181.62840277778</v>
-      </c>
-      <c r="I7" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="1" t="s">
+        <v>46184.333379629628</v>
+      </c>
+      <c r="I7" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="5">
         <v>2026</v>
       </c>
       <c r="D8" s="10">
         <v>24</v>
       </c>
-      <c r="E8" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F8" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G8" s="11">
-        <v>18593</v>
+      <c r="E8" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F8" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G8" s="5">
+        <v>19080</v>
       </c>
       <c r="H8" s="12">
-        <v>46184.333379629628</v>
-      </c>
-      <c r="I8" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="10" t="s">
+        <v>46191.333344907405</v>
+      </c>
+      <c r="I8" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="11">
         <v>2026</v>
       </c>
       <c r="D9" s="10">
         <v>24</v>
       </c>
-      <c r="E9" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F9" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G9" s="5">
-        <v>19080</v>
+      <c r="E9" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F9" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G9" s="11">
+        <v>17252</v>
       </c>
       <c r="H9" s="12">
-        <v>46191.333344907405</v>
-      </c>
-      <c r="I9" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="1" t="s">
+        <v>46163.708333333336</v>
+      </c>
+      <c r="I9" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="5">
         <v>2026</v>
       </c>
       <c r="D10" s="10">
         <v>24</v>
       </c>
-      <c r="E10" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F10" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G10" s="11">
-        <v>17252</v>
+      <c r="E10" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F10" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G10" s="5">
+        <v>18006</v>
       </c>
       <c r="H10" s="12">
-        <v>46163.708333333336</v>
-      </c>
-      <c r="I10" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="10" t="s">
+        <v>46175.708333333336</v>
+      </c>
+      <c r="I10" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1019,25 +990,25 @@
       <c r="D11" s="10">
         <v>24</v>
       </c>
-      <c r="E11" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="E11" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F11" s="16">
         <v>46199</v>
       </c>
       <c r="G11" s="5">
-        <v>18006</v>
+        <v>18333</v>
       </c>
       <c r="H11" s="12">
-        <v>46175.708333333336</v>
-      </c>
-      <c r="I11" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="1" t="s">
+        <v>46178.44940972222</v>
+      </c>
+      <c r="I11" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1054,25 +1025,25 @@
       <c r="D12" s="10">
         <v>24</v>
       </c>
-      <c r="E12" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F12" s="14">
+      <c r="E12" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F12" s="16">
         <v>46199</v>
       </c>
       <c r="G12" s="5">
-        <v>18333</v>
+        <v>18385</v>
       </c>
       <c r="H12" s="12">
-        <v>46178.44940972222</v>
-      </c>
-      <c r="I12" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="10" t="s">
+        <v>46177.666134259256</v>
+      </c>
+      <c r="I12" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1089,22 +1060,22 @@
       <c r="D13" s="10">
         <v>24</v>
       </c>
-      <c r="E13" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="E13" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F13" s="16">
         <v>46199</v>
       </c>
       <c r="G13" s="5">
-        <v>18385</v>
+        <v>18403</v>
       </c>
       <c r="H13" s="12">
-        <v>46177.666134259256</v>
-      </c>
-      <c r="I13" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J13" s="11" t="s">
+        <v>46178.708333333336</v>
+      </c>
+      <c r="I13" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -1124,22 +1095,22 @@
       <c r="D14" s="10">
         <v>24</v>
       </c>
-      <c r="E14" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="E14" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F14" s="16">
         <v>46199</v>
       </c>
       <c r="G14" s="5">
-        <v>18403</v>
+        <v>18434</v>
       </c>
       <c r="H14" s="12">
-        <v>46178.708333333336</v>
-      </c>
-      <c r="I14" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J14" s="11" t="s">
+        <v>46181.369317129633</v>
+      </c>
+      <c r="I14" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -1159,22 +1130,22 @@
       <c r="D15" s="10">
         <v>24</v>
       </c>
-      <c r="E15" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="E15" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F15" s="16">
         <v>46199</v>
       </c>
       <c r="G15" s="5">
-        <v>18434</v>
+        <v>18450</v>
       </c>
       <c r="H15" s="12">
-        <v>46181.369317129633</v>
-      </c>
-      <c r="I15" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J15" s="11" t="s">
+        <v>46181.445613425924</v>
+      </c>
+      <c r="I15" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J15" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -1194,22 +1165,22 @@
       <c r="D16" s="10">
         <v>24</v>
       </c>
-      <c r="E16" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="E16" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F16" s="16">
         <v>46199</v>
       </c>
       <c r="G16" s="5">
-        <v>18450</v>
+        <v>18460</v>
       </c>
       <c r="H16" s="12">
-        <v>46181.445613425924</v>
-      </c>
-      <c r="I16" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J16" s="11" t="s">
+        <v>46181.507349537038</v>
+      </c>
+      <c r="I16" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1221,65 +1192,65 @@
         <v>3</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="10">
+        <v>24</v>
+      </c>
+      <c r="E17" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F17" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G17" s="5">
+        <v>18489</v>
+      </c>
+      <c r="H17" s="12">
+        <v>46181.640405092592</v>
+      </c>
+      <c r="I17" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="10">
-        <v>24</v>
-      </c>
-      <c r="E17" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F17" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G17" s="5">
-        <v>18460</v>
-      </c>
-      <c r="H17" s="12">
-        <v>46181.507349537038</v>
-      </c>
-      <c r="I17" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="C18" s="11">
         <v>2026</v>
       </c>
       <c r="D18" s="10">
         <v>24</v>
       </c>
-      <c r="E18" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F18" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G18" s="5">
-        <v>18489</v>
+      <c r="E18" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F18" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G18" s="11">
+        <v>18501</v>
       </c>
       <c r="H18" s="12">
-        <v>46181.640405092592</v>
-      </c>
-      <c r="I18" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J18" s="11" t="s">
+        <v>46181.686215277776</v>
+      </c>
+      <c r="I18" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J18" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K18" s="10" t="s">
@@ -1287,37 +1258,37 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="5">
         <v>2026</v>
       </c>
       <c r="D19" s="10">
         <v>24</v>
       </c>
-      <c r="E19" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F19" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G19" s="11">
-        <v>18501</v>
+      <c r="E19" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F19" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G19" s="5">
+        <v>18664</v>
       </c>
       <c r="H19" s="12">
-        <v>46181.686215277776</v>
-      </c>
-      <c r="I19" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="10" t="s">
+        <v>46184.611759259256</v>
+      </c>
+      <c r="I19" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1334,22 +1305,22 @@
       <c r="D20" s="10">
         <v>24</v>
       </c>
-      <c r="E20" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="E20" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F20" s="16">
         <v>46199</v>
       </c>
       <c r="G20" s="5">
-        <v>18664</v>
+        <v>18749</v>
       </c>
       <c r="H20" s="12">
-        <v>46184.611759259256</v>
-      </c>
-      <c r="I20" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J20" s="11" t="s">
+        <v>46185.49927083333</v>
+      </c>
+      <c r="I20" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -1369,22 +1340,22 @@
       <c r="D21" s="10">
         <v>24</v>
       </c>
-      <c r="E21" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F21" s="14">
+      <c r="E21" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F21" s="16">
         <v>46199</v>
       </c>
       <c r="G21" s="5">
-        <v>18749</v>
+        <v>18754</v>
       </c>
       <c r="H21" s="12">
-        <v>46185.49927083333</v>
-      </c>
-      <c r="I21" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J21" s="11" t="s">
+        <v>46185.554965277777</v>
+      </c>
+      <c r="I21" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -1404,22 +1375,22 @@
       <c r="D22" s="10">
         <v>24</v>
       </c>
-      <c r="E22" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F22" s="14">
+      <c r="E22" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F22" s="16">
         <v>46199</v>
       </c>
       <c r="G22" s="5">
-        <v>18754</v>
+        <v>18775</v>
       </c>
       <c r="H22" s="12">
-        <v>46185.554965277777</v>
-      </c>
-      <c r="I22" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J22" s="11" t="s">
+        <v>46184.678923611114</v>
+      </c>
+      <c r="I22" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -1439,22 +1410,22 @@
       <c r="D23" s="10">
         <v>24</v>
       </c>
-      <c r="E23" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F23" s="14">
+      <c r="E23" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F23" s="16">
         <v>46199</v>
       </c>
       <c r="G23" s="5">
-        <v>18775</v>
+        <v>18780</v>
       </c>
       <c r="H23" s="12">
-        <v>46184.678923611114</v>
-      </c>
-      <c r="I23" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J23" s="11" t="s">
+        <v>46185.691631944443</v>
+      </c>
+      <c r="I23" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -1474,23 +1445,23 @@
       <c r="D24" s="10">
         <v>24</v>
       </c>
-      <c r="E24" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F24" s="14">
+      <c r="E24" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F24" s="16">
         <v>46199</v>
       </c>
       <c r="G24" s="5">
-        <v>18780</v>
+        <v>18783</v>
       </c>
       <c r="H24" s="12">
-        <v>46185.691631944443</v>
-      </c>
-      <c r="I24" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>13</v>
+        <v>46185.708333333336</v>
+      </c>
+      <c r="I24" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>12</v>
@@ -1509,23 +1480,23 @@
       <c r="D25" s="10">
         <v>24</v>
       </c>
-      <c r="E25" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F25" s="14">
+      <c r="E25" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F25" s="16">
         <v>46199</v>
       </c>
       <c r="G25" s="5">
-        <v>18783</v>
+        <v>18897</v>
       </c>
       <c r="H25" s="12">
-        <v>46185.708333333336</v>
-      </c>
-      <c r="I25" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>13</v>
+        <v>46189.376655092594</v>
+      </c>
+      <c r="I25" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>12</v>
@@ -1544,22 +1515,22 @@
       <c r="D26" s="10">
         <v>24</v>
       </c>
-      <c r="E26" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F26" s="14">
+      <c r="E26" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F26" s="16">
         <v>46199</v>
       </c>
       <c r="G26" s="5">
-        <v>18897</v>
+        <v>18911</v>
       </c>
       <c r="H26" s="12">
-        <v>46189.376655092594</v>
-      </c>
-      <c r="I26" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J26" s="11" t="s">
+        <v>46189.448611111111</v>
+      </c>
+      <c r="I26" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -1567,37 +1538,37 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="11">
         <v>2026</v>
       </c>
       <c r="D27" s="10">
         <v>24</v>
       </c>
-      <c r="E27" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F27" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G27" s="5">
-        <v>18911</v>
+      <c r="E27" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F27" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G27" s="11">
+        <v>18942</v>
       </c>
       <c r="H27" s="12">
-        <v>46189.448611111111</v>
-      </c>
-      <c r="I27" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="1" t="s">
+        <v>46189.612326388888</v>
+      </c>
+      <c r="I27" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1614,22 +1585,22 @@
       <c r="D28" s="10">
         <v>24</v>
       </c>
-      <c r="E28" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="E28" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F28" s="16">
         <v>46199</v>
       </c>
       <c r="G28" s="11">
-        <v>18942</v>
+        <v>19032</v>
       </c>
       <c r="H28" s="12">
-        <v>46189.612326388888</v>
-      </c>
-      <c r="I28" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J28" s="11" t="s">
+        <v>46190.688344907408</v>
+      </c>
+      <c r="I28" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J28" s="14" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="10" t="s">
@@ -1641,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C29" s="11">
         <v>2026</v>
@@ -1649,67 +1620,32 @@
       <c r="D29" s="10">
         <v>24</v>
       </c>
-      <c r="E29" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F29" s="14">
+      <c r="E29" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F29" s="16">
         <v>46199</v>
       </c>
       <c r="G29" s="11">
-        <v>19032</v>
+        <v>18994</v>
       </c>
       <c r="H29" s="12">
-        <v>46190.688344907408</v>
-      </c>
-      <c r="I29" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>13</v>
+        <v>46189.696238425924</v>
+      </c>
+      <c r="I29" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D30" s="10">
-        <v>24</v>
-      </c>
-      <c r="E30" s="14">
-        <v>46195</v>
-      </c>
-      <c r="F30" s="14">
-        <v>46199</v>
-      </c>
-      <c r="G30" s="11">
-        <v>18994</v>
-      </c>
-      <c r="H30" s="12">
-        <v>46189.696238425924</v>
-      </c>
-      <c r="I30" s="14">
-        <v>46195</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K32" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K30">
-      <sortCondition ref="B1:B32"/>
+  <autoFilter ref="A1:K31" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K29">
+      <sortCondition ref="B1:B31"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1719,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
@@ -1771,17 +1707,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="C2" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="10">
         <v>24</v>
       </c>
       <c r="E2" s="16">
@@ -1790,7 +1726,7 @@
       <c r="F2" s="16">
         <v>46199</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="10">
         <v>19077</v>
       </c>
       <c r="H2" s="17">
@@ -1799,94 +1735,94 @@
       <c r="I2" s="16">
         <v>46195</v>
       </c>
-      <c r="J2" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="J2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="19">
-        <v>24</v>
-      </c>
-      <c r="E3" s="20">
-        <v>46195</v>
-      </c>
-      <c r="F3" s="20">
-        <v>46199</v>
-      </c>
-      <c r="G3" s="19">
+      <c r="C3" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="10">
+        <v>24</v>
+      </c>
+      <c r="E3" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F3" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G3" s="10">
         <v>19203</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="17">
         <v>46192.575902777775</v>
       </c>
-      <c r="I3" s="20">
-        <v>46195</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="I3" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="19">
-        <v>24</v>
-      </c>
-      <c r="E4" s="20">
-        <v>46195</v>
-      </c>
-      <c r="F4" s="20">
-        <v>46199</v>
-      </c>
-      <c r="G4" s="19">
+      <c r="C4" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="10">
+        <v>24</v>
+      </c>
+      <c r="E4" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F4" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G4" s="10">
         <v>19213</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="17">
         <v>46192.708333333336</v>
       </c>
-      <c r="I4" s="20">
-        <v>46195</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="15" t="s">
+      <c r="I4" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="10">
         <v>24</v>
       </c>
       <c r="E5" s="16">
@@ -1895,7 +1831,7 @@
       <c r="F5" s="16">
         <v>46199</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="10">
         <v>19214</v>
       </c>
       <c r="H5" s="17">
@@ -1904,24 +1840,24 @@
       <c r="I5" s="16">
         <v>46195</v>
       </c>
-      <c r="J5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="15" t="s">
+      <c r="J5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="10">
         <v>24</v>
       </c>
       <c r="E6" s="16">
@@ -1930,7 +1866,7 @@
       <c r="F6" s="16">
         <v>46199</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="10">
         <v>19236</v>
       </c>
       <c r="H6" s="17">
@@ -1939,24 +1875,24 @@
       <c r="I6" s="16">
         <v>46195</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="J6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="10">
         <v>24</v>
       </c>
       <c r="E7" s="16">
@@ -1965,7 +1901,7 @@
       <c r="F7" s="16">
         <v>46199</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="10">
         <v>19237</v>
       </c>
       <c r="H7" s="17">
@@ -1974,24 +1910,24 @@
       <c r="I7" s="16">
         <v>46195</v>
       </c>
-      <c r="J7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="15" t="s">
+      <c r="J7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="10">
         <v>24</v>
       </c>
       <c r="E8" s="16">
@@ -2000,7 +1936,7 @@
       <c r="F8" s="16">
         <v>46199</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="10">
         <v>19266</v>
       </c>
       <c r="H8" s="17">
@@ -2009,24 +1945,24 @@
       <c r="I8" s="16">
         <v>46195</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="15" t="s">
+      <c r="J8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="10">
         <v>24</v>
       </c>
       <c r="E9" s="16">
@@ -2035,7 +1971,7 @@
       <c r="F9" s="16">
         <v>46199</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="10">
         <v>19281</v>
       </c>
       <c r="H9" s="17">
@@ -2044,24 +1980,24 @@
       <c r="I9" s="16">
         <v>46195</v>
       </c>
-      <c r="J9" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="J9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="10">
         <v>24</v>
       </c>
       <c r="E10" s="16">
@@ -2070,7 +2006,7 @@
       <c r="F10" s="16">
         <v>46199</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="10">
         <v>17306</v>
       </c>
       <c r="H10" s="17">
@@ -2079,24 +2015,24 @@
       <c r="I10" s="16">
         <v>46195</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="15" t="s">
+      <c r="J10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="10">
         <v>24</v>
       </c>
       <c r="E11" s="16">
@@ -2105,7 +2041,7 @@
       <c r="F11" s="16">
         <v>46199</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="10">
         <v>17195</v>
       </c>
       <c r="H11" s="17">
@@ -2114,24 +2050,24 @@
       <c r="I11" s="16">
         <v>46195</v>
       </c>
-      <c r="J11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="15" t="s">
+      <c r="J11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="C12" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="10">
         <v>24</v>
       </c>
       <c r="E12" s="16">
@@ -2140,7 +2076,7 @@
       <c r="F12" s="16">
         <v>46199</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="10">
         <v>17382</v>
       </c>
       <c r="H12" s="17">
@@ -2149,24 +2085,24 @@
       <c r="I12" s="16">
         <v>46195</v>
       </c>
-      <c r="J12" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="15" t="s">
+      <c r="J12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="10">
         <v>24</v>
       </c>
       <c r="E13" s="16">
@@ -2175,7 +2111,7 @@
       <c r="F13" s="16">
         <v>46199</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="10">
         <v>18490</v>
       </c>
       <c r="H13" s="17">
@@ -2184,24 +2120,24 @@
       <c r="I13" s="16">
         <v>46195</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="15" t="s">
+      <c r="J13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="C14" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="10">
         <v>24</v>
       </c>
       <c r="E14" s="16">
@@ -2210,7 +2146,7 @@
       <c r="F14" s="16">
         <v>46199</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="10">
         <v>18626</v>
       </c>
       <c r="H14" s="17">
@@ -2219,24 +2155,24 @@
       <c r="I14" s="16">
         <v>46195</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="15" t="s">
+      <c r="J14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="10">
         <v>24</v>
       </c>
       <c r="E15" s="16">
@@ -2245,7 +2181,7 @@
       <c r="F15" s="16">
         <v>46199</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="10">
         <v>18649</v>
       </c>
       <c r="H15" s="17">
@@ -2254,24 +2190,24 @@
       <c r="I15" s="16">
         <v>46195</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="15" t="s">
+      <c r="J15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="10">
         <v>24</v>
       </c>
       <c r="E16" s="16">
@@ -2280,7 +2216,7 @@
       <c r="F16" s="16">
         <v>46199</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="10">
         <v>19205</v>
       </c>
       <c r="H16" s="17">
@@ -2289,24 +2225,24 @@
       <c r="I16" s="16">
         <v>46195</v>
       </c>
-      <c r="J16" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="J16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="10">
         <v>24</v>
       </c>
       <c r="E17" s="16">
@@ -2315,7 +2251,7 @@
       <c r="F17" s="16">
         <v>46199</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="10">
         <v>19254</v>
       </c>
       <c r="H17" s="17">
@@ -2324,24 +2260,24 @@
       <c r="I17" s="16">
         <v>46195</v>
       </c>
-      <c r="J17" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="15" t="s">
+      <c r="J17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="10">
         <v>24</v>
       </c>
       <c r="E18" s="16">
@@ -2350,7 +2286,7 @@
       <c r="F18" s="16">
         <v>46199</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="10">
         <v>19293</v>
       </c>
       <c r="H18" s="17">
@@ -2359,24 +2295,24 @@
       <c r="I18" s="16">
         <v>46195</v>
       </c>
-      <c r="J18" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="15" t="s">
+      <c r="J18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="10">
         <v>24</v>
       </c>
       <c r="E19" s="16">
@@ -2385,7 +2321,7 @@
       <c r="F19" s="16">
         <v>46199</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="10">
         <v>19386</v>
       </c>
       <c r="H19" s="17">
@@ -2394,24 +2330,24 @@
       <c r="I19" s="16">
         <v>46195</v>
       </c>
-      <c r="J19" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="15" t="s">
+      <c r="J19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="K19" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="10">
         <v>24</v>
       </c>
       <c r="E20" s="16">
@@ -2420,7 +2356,7 @@
       <c r="F20" s="16">
         <v>46199</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="10">
         <v>19131</v>
       </c>
       <c r="H20" s="17">
@@ -2429,24 +2365,24 @@
       <c r="I20" s="16">
         <v>46195</v>
       </c>
-      <c r="J20" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="15" t="s">
+      <c r="J20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="K20" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="10">
         <v>24</v>
       </c>
       <c r="E21" s="16">
@@ -2455,7 +2391,7 @@
       <c r="F21" s="16">
         <v>46199</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="10">
         <v>19195</v>
       </c>
       <c r="H21" s="17">
@@ -2464,24 +2400,24 @@
       <c r="I21" s="16">
         <v>46195</v>
       </c>
-      <c r="J21" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="15" t="s">
+      <c r="J21" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="10">
         <v>24</v>
       </c>
       <c r="E22" s="16">
@@ -2490,7 +2426,7 @@
       <c r="F22" s="16">
         <v>46199</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="10">
         <v>17234</v>
       </c>
       <c r="H22" s="17">
@@ -2499,24 +2435,24 @@
       <c r="I22" s="16">
         <v>46195</v>
       </c>
-      <c r="J22" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="15" t="s">
+      <c r="J22" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="10">
         <v>24</v>
       </c>
       <c r="E23" s="16">
@@ -2525,7 +2461,7 @@
       <c r="F23" s="16">
         <v>46199</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="10">
         <v>19090</v>
       </c>
       <c r="H23" s="17">
@@ -2534,24 +2470,24 @@
       <c r="I23" s="16">
         <v>46195</v>
       </c>
-      <c r="J23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="15" t="s">
+      <c r="J23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="15">
+      <c r="C24" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="10">
         <v>24</v>
       </c>
       <c r="E24" s="16">
@@ -2560,7 +2496,7 @@
       <c r="F24" s="16">
         <v>46199</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="10">
         <v>19234</v>
       </c>
       <c r="H24" s="17">
@@ -2569,24 +2505,24 @@
       <c r="I24" s="16">
         <v>46195</v>
       </c>
-      <c r="J24" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="15" t="s">
+      <c r="J24" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="10">
         <v>24</v>
       </c>
       <c r="E25" s="16">
@@ -2595,7 +2531,7 @@
       <c r="F25" s="16">
         <v>46199</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="10">
         <v>17640</v>
       </c>
       <c r="H25" s="17">
@@ -2604,24 +2540,24 @@
       <c r="I25" s="16">
         <v>46195</v>
       </c>
-      <c r="J25" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="15" t="s">
+      <c r="J25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="10">
         <v>24</v>
       </c>
       <c r="E26" s="16">
@@ -2630,7 +2566,7 @@
       <c r="F26" s="16">
         <v>46199</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="10">
         <v>19211</v>
       </c>
       <c r="H26" s="17">
@@ -2639,24 +2575,24 @@
       <c r="I26" s="16">
         <v>46195</v>
       </c>
-      <c r="J26" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="15" t="s">
+      <c r="J26" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="10">
         <v>24</v>
       </c>
       <c r="E27" s="16">
@@ -2665,7 +2601,7 @@
       <c r="F27" s="16">
         <v>46199</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="10">
         <v>19093</v>
       </c>
       <c r="H27" s="17">
@@ -2674,24 +2610,24 @@
       <c r="I27" s="16">
         <v>46195</v>
       </c>
-      <c r="J27" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="15" t="s">
+      <c r="J27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D28" s="10">
         <v>24</v>
       </c>
       <c r="E28" s="16">
@@ -2700,7 +2636,7 @@
       <c r="F28" s="16">
         <v>46199</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="10">
         <v>18188</v>
       </c>
       <c r="H28" s="17">
@@ -2709,24 +2645,24 @@
       <c r="I28" s="16">
         <v>46195</v>
       </c>
-      <c r="J28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="15" t="s">
+      <c r="J28" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D29" s="10">
         <v>24</v>
       </c>
       <c r="E29" s="16">
@@ -2735,7 +2671,7 @@
       <c r="F29" s="16">
         <v>46199</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="10">
         <v>18650</v>
       </c>
       <c r="H29" s="17">
@@ -2744,24 +2680,24 @@
       <c r="I29" s="16">
         <v>46195</v>
       </c>
-      <c r="J29" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="15" t="s">
+      <c r="J29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D30" s="15">
+      <c r="C30" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="10">
         <v>24</v>
       </c>
       <c r="E30" s="16">
@@ -2770,7 +2706,7 @@
       <c r="F30" s="16">
         <v>46199</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="10">
         <v>18927</v>
       </c>
       <c r="H30" s="17">
@@ -2779,24 +2715,24 @@
       <c r="I30" s="16">
         <v>46195</v>
       </c>
-      <c r="J30" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="15" t="s">
+      <c r="J30" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="10">
         <v>24</v>
       </c>
       <c r="E31" s="16">
@@ -2805,7 +2741,7 @@
       <c r="F31" s="16">
         <v>46199</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="10">
         <v>19235</v>
       </c>
       <c r="H31" s="17">
@@ -2814,24 +2750,24 @@
       <c r="I31" s="16">
         <v>46195</v>
       </c>
-      <c r="J31" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="15" t="s">
+      <c r="J31" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D32" s="15">
+      <c r="C32" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D32" s="10">
         <v>24</v>
       </c>
       <c r="E32" s="16">
@@ -2840,7 +2776,7 @@
       <c r="F32" s="16">
         <v>46199</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="10">
         <v>19257</v>
       </c>
       <c r="H32" s="17">
@@ -2849,10 +2785,45 @@
       <c r="I32" s="16">
         <v>46195</v>
       </c>
-      <c r="J32" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="15" t="s">
+      <c r="J32" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D33" s="10">
+        <v>24</v>
+      </c>
+      <c r="E33" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F33" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G33" s="11">
+        <v>19299</v>
+      </c>
+      <c r="H33" s="12">
+        <v>46195.583402777775</v>
+      </c>
+      <c r="I33" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/base/Backlog_24.xlsx
+++ b/data/base/Backlog_24.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17BDCCFE-83C6-44CA-9B53-8B90B8C1C356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9980D33A-F2C3-4CEA-A177-B9345CFC09AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -615,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="6" customWidth="1"/>
@@ -667,7 +667,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5">
         <v>2026</v>
@@ -682,27 +682,27 @@
         <v>46199</v>
       </c>
       <c r="G2" s="5">
-        <v>16819</v>
+        <v>18276</v>
       </c>
       <c r="H2" s="12">
-        <v>46157.643171296295</v>
+        <v>46177.708333333336</v>
       </c>
       <c r="I2" s="16">
         <v>46195</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="5">
         <v>2026</v>
@@ -717,29 +717,29 @@
         <v>46199</v>
       </c>
       <c r="G3" s="5">
-        <v>18346</v>
+        <v>18485</v>
       </c>
       <c r="H3" s="12">
-        <v>46178.538541666669</v>
+        <v>46181.62840277778</v>
       </c>
       <c r="I3" s="16">
         <v>46195</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="11">
         <v>2026</v>
       </c>
       <c r="D4" s="10">
@@ -751,28 +751,28 @@
       <c r="F4" s="16">
         <v>46199</v>
       </c>
-      <c r="G4" s="5">
-        <v>18418</v>
+      <c r="G4" s="11">
+        <v>18593</v>
       </c>
       <c r="H4" s="12">
-        <v>46178.708333333336</v>
+        <v>46184.333379629628</v>
       </c>
       <c r="I4" s="16">
         <v>46195</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5">
         <v>2026</v>
@@ -787,10 +787,10 @@
         <v>46199</v>
       </c>
       <c r="G5" s="5">
-        <v>18276</v>
+        <v>19080</v>
       </c>
       <c r="H5" s="12">
-        <v>46177.708333333336</v>
+        <v>46191.333344907405</v>
       </c>
       <c r="I5" s="16">
         <v>46195</v>
@@ -803,13 +803,13 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11">
         <v>2026</v>
       </c>
       <c r="D6" s="10">
@@ -821,30 +821,30 @@
       <c r="F6" s="16">
         <v>46199</v>
       </c>
-      <c r="G6" s="5">
-        <v>18485</v>
+      <c r="G6" s="11">
+        <v>17252</v>
       </c>
       <c r="H6" s="12">
-        <v>46181.62840277778</v>
+        <v>46163.708333333336</v>
       </c>
       <c r="I6" s="16">
         <v>46195</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5">
         <v>2026</v>
       </c>
       <c r="D7" s="10">
@@ -856,11 +856,11 @@
       <c r="F7" s="16">
         <v>46199</v>
       </c>
-      <c r="G7" s="11">
-        <v>18593</v>
+      <c r="G7" s="5">
+        <v>18006</v>
       </c>
       <c r="H7" s="12">
-        <v>46184.333379629628</v>
+        <v>46175.708333333336</v>
       </c>
       <c r="I7" s="16">
         <v>46195</v>
@@ -868,7 +868,7 @@
       <c r="J7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -877,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5">
         <v>2026</v>
@@ -892,29 +892,29 @@
         <v>46199</v>
       </c>
       <c r="G8" s="5">
-        <v>19080</v>
+        <v>18333</v>
       </c>
       <c r="H8" s="12">
-        <v>46191.333344907405</v>
+        <v>46178.44940972222</v>
       </c>
       <c r="I8" s="16">
         <v>46195</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="5">
         <v>2026</v>
       </c>
       <c r="D9" s="10">
@@ -926,11 +926,11 @@
       <c r="F9" s="16">
         <v>46199</v>
       </c>
-      <c r="G9" s="11">
-        <v>17252</v>
+      <c r="G9" s="5">
+        <v>18385</v>
       </c>
       <c r="H9" s="12">
-        <v>46163.708333333336</v>
+        <v>46177.666134259256</v>
       </c>
       <c r="I9" s="16">
         <v>46195</v>
@@ -938,7 +938,7 @@
       <c r="J9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -962,16 +962,16 @@
         <v>46199</v>
       </c>
       <c r="G10" s="5">
-        <v>18006</v>
+        <v>18403</v>
       </c>
       <c r="H10" s="12">
-        <v>46175.708333333336</v>
+        <v>46178.708333333336</v>
       </c>
       <c r="I10" s="16">
         <v>46195</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>12</v>
@@ -997,10 +997,10 @@
         <v>46199</v>
       </c>
       <c r="G11" s="5">
-        <v>18333</v>
+        <v>18434</v>
       </c>
       <c r="H11" s="12">
-        <v>46178.44940972222</v>
+        <v>46181.369317129633</v>
       </c>
       <c r="I11" s="16">
         <v>46195</v>
@@ -1008,7 +1008,7 @@
       <c r="J11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1032,10 +1032,10 @@
         <v>46199</v>
       </c>
       <c r="G12" s="5">
-        <v>18385</v>
+        <v>18450</v>
       </c>
       <c r="H12" s="12">
-        <v>46177.666134259256</v>
+        <v>46181.445613425924</v>
       </c>
       <c r="I12" s="16">
         <v>46195</v>
@@ -1067,10 +1067,10 @@
         <v>46199</v>
       </c>
       <c r="G13" s="5">
-        <v>18403</v>
+        <v>18460</v>
       </c>
       <c r="H13" s="12">
-        <v>46178.708333333336</v>
+        <v>46181.507349537038</v>
       </c>
       <c r="I13" s="16">
         <v>46195</v>
@@ -1087,44 +1087,44 @@
         <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="10">
+        <v>24</v>
+      </c>
+      <c r="E14" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F14" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G14" s="5">
+        <v>18489</v>
+      </c>
+      <c r="H14" s="12">
+        <v>46181.640405092592</v>
+      </c>
+      <c r="I14" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="10">
-        <v>24</v>
-      </c>
-      <c r="E14" s="16">
-        <v>46195</v>
-      </c>
-      <c r="F14" s="16">
-        <v>46199</v>
-      </c>
-      <c r="G14" s="5">
-        <v>18434</v>
-      </c>
-      <c r="H14" s="12">
-        <v>46181.369317129633</v>
-      </c>
-      <c r="I14" s="16">
-        <v>46195</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="C15" s="11">
         <v>2026</v>
       </c>
       <c r="D15" s="10">
@@ -1136,11 +1136,11 @@
       <c r="F15" s="16">
         <v>46199</v>
       </c>
-      <c r="G15" s="5">
-        <v>18450</v>
+      <c r="G15" s="11">
+        <v>18501</v>
       </c>
       <c r="H15" s="12">
-        <v>46181.445613425924</v>
+        <v>46181.686215277776</v>
       </c>
       <c r="I15" s="16">
         <v>46195</v>
@@ -1148,7 +1148,7 @@
       <c r="J15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1172,10 +1172,10 @@
         <v>46199</v>
       </c>
       <c r="G16" s="5">
-        <v>18460</v>
+        <v>18664</v>
       </c>
       <c r="H16" s="12">
-        <v>46181.507349537038</v>
+        <v>46184.611759259256</v>
       </c>
       <c r="I16" s="16">
         <v>46195</v>
@@ -1192,7 +1192,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C17" s="5">
         <v>2026</v>
@@ -1207,10 +1207,10 @@
         <v>46199</v>
       </c>
       <c r="G17" s="5">
-        <v>18489</v>
+        <v>18749</v>
       </c>
       <c r="H17" s="12">
-        <v>46181.640405092592</v>
+        <v>46185.49927083333</v>
       </c>
       <c r="I17" s="16">
         <v>46195</v>
@@ -1218,18 +1218,18 @@
       <c r="J17" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="5">
         <v>2026</v>
       </c>
       <c r="D18" s="10">
@@ -1241,11 +1241,11 @@
       <c r="F18" s="16">
         <v>46199</v>
       </c>
-      <c r="G18" s="11">
-        <v>18501</v>
+      <c r="G18" s="5">
+        <v>18754</v>
       </c>
       <c r="H18" s="12">
-        <v>46181.686215277776</v>
+        <v>46185.554965277777</v>
       </c>
       <c r="I18" s="16">
         <v>46195</v>
@@ -1253,7 +1253,7 @@
       <c r="J18" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1277,10 +1277,10 @@
         <v>46199</v>
       </c>
       <c r="G19" s="5">
-        <v>18664</v>
+        <v>18775</v>
       </c>
       <c r="H19" s="12">
-        <v>46184.611759259256</v>
+        <v>46184.678923611114</v>
       </c>
       <c r="I19" s="16">
         <v>46195</v>
@@ -1312,10 +1312,10 @@
         <v>46199</v>
       </c>
       <c r="G20" s="5">
-        <v>18749</v>
+        <v>18780</v>
       </c>
       <c r="H20" s="12">
-        <v>46185.49927083333</v>
+        <v>46185.691631944443</v>
       </c>
       <c r="I20" s="16">
         <v>46195</v>
@@ -1347,16 +1347,16 @@
         <v>46199</v>
       </c>
       <c r="G21" s="5">
-        <v>18754</v>
+        <v>18783</v>
       </c>
       <c r="H21" s="12">
-        <v>46185.554965277777</v>
+        <v>46185.708333333336</v>
       </c>
       <c r="I21" s="16">
         <v>46195</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>12</v>
@@ -1382,16 +1382,16 @@
         <v>46199</v>
       </c>
       <c r="G22" s="5">
-        <v>18775</v>
+        <v>18897</v>
       </c>
       <c r="H22" s="12">
-        <v>46184.678923611114</v>
+        <v>46189.376655092594</v>
       </c>
       <c r="I22" s="16">
         <v>46195</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>12</v>
@@ -1417,10 +1417,10 @@
         <v>46199</v>
       </c>
       <c r="G23" s="5">
-        <v>18780</v>
+        <v>18911</v>
       </c>
       <c r="H23" s="12">
-        <v>46185.691631944443</v>
+        <v>46189.448611111111</v>
       </c>
       <c r="I23" s="16">
         <v>46195</v>
@@ -1433,13 +1433,13 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="11">
         <v>2026</v>
       </c>
       <c r="D24" s="10">
@@ -1451,201 +1451,96 @@
       <c r="F24" s="16">
         <v>46199</v>
       </c>
-      <c r="G24" s="5">
-        <v>18783</v>
+      <c r="G24" s="11">
+        <v>18942</v>
       </c>
       <c r="H24" s="12">
-        <v>46185.708333333336</v>
+        <v>46189.612326388888</v>
       </c>
       <c r="I24" s="16">
         <v>46195</v>
       </c>
       <c r="J24" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="10">
+        <v>24</v>
+      </c>
+      <c r="E25" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F25" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G25" s="11">
+        <v>19032</v>
+      </c>
+      <c r="H25" s="12">
+        <v>46190.688344907408</v>
+      </c>
+      <c r="I25" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="10">
+        <v>24</v>
+      </c>
+      <c r="E26" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F26" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G26" s="11">
+        <v>18994</v>
+      </c>
+      <c r="H26" s="12">
+        <v>46189.696238425924</v>
+      </c>
+      <c r="I26" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K26" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="10">
-        <v>24</v>
-      </c>
-      <c r="E25" s="16">
-        <v>46195</v>
-      </c>
-      <c r="F25" s="16">
-        <v>46199</v>
-      </c>
-      <c r="G25" s="5">
-        <v>18897</v>
-      </c>
-      <c r="H25" s="12">
-        <v>46189.376655092594</v>
-      </c>
-      <c r="I25" s="16">
-        <v>46195</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="10">
-        <v>24</v>
-      </c>
-      <c r="E26" s="16">
-        <v>46195</v>
-      </c>
-      <c r="F26" s="16">
-        <v>46199</v>
-      </c>
-      <c r="G26" s="5">
-        <v>18911</v>
-      </c>
-      <c r="H26" s="12">
-        <v>46189.448611111111</v>
-      </c>
-      <c r="I26" s="16">
-        <v>46195</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="10">
-        <v>24</v>
-      </c>
-      <c r="E27" s="16">
-        <v>46195</v>
-      </c>
-      <c r="F27" s="16">
-        <v>46199</v>
-      </c>
-      <c r="G27" s="11">
-        <v>18942</v>
-      </c>
-      <c r="H27" s="12">
-        <v>46189.612326388888</v>
-      </c>
-      <c r="I27" s="16">
-        <v>46195</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D28" s="10">
-        <v>24</v>
-      </c>
-      <c r="E28" s="16">
-        <v>46195</v>
-      </c>
-      <c r="F28" s="16">
-        <v>46199</v>
-      </c>
-      <c r="G28" s="11">
-        <v>19032</v>
-      </c>
-      <c r="H28" s="12">
-        <v>46190.688344907408</v>
-      </c>
-      <c r="I28" s="16">
-        <v>46195</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D29" s="10">
-        <v>24</v>
-      </c>
-      <c r="E29" s="16">
-        <v>46195</v>
-      </c>
-      <c r="F29" s="16">
-        <v>46199</v>
-      </c>
-      <c r="G29" s="11">
-        <v>18994</v>
-      </c>
-      <c r="H29" s="12">
-        <v>46189.696238425924</v>
-      </c>
-      <c r="I29" s="16">
-        <v>46195</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K31" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K29">
-      <sortCondition ref="B1:B31"/>
+  <autoFilter ref="A1:K28" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+      <sortCondition ref="B1:B28"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1655,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
@@ -2825,6 +2720,111 @@
       </c>
       <c r="K33" s="10" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D34" s="10">
+        <v>24</v>
+      </c>
+      <c r="E34" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F34" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G34" s="5">
+        <v>16819</v>
+      </c>
+      <c r="H34" s="12">
+        <v>46157.643171296295</v>
+      </c>
+      <c r="I34" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D35" s="10">
+        <v>24</v>
+      </c>
+      <c r="E35" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F35" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G35" s="5">
+        <v>18346</v>
+      </c>
+      <c r="H35" s="12">
+        <v>46178.538541666669</v>
+      </c>
+      <c r="I35" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D36" s="10">
+        <v>24</v>
+      </c>
+      <c r="E36" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F36" s="16">
+        <v>46199</v>
+      </c>
+      <c r="G36" s="5">
+        <v>18418</v>
+      </c>
+      <c r="H36" s="12">
+        <v>46178.708333333336</v>
+      </c>
+      <c r="I36" s="16">
+        <v>46195</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
